--- a/StructureDefinition-ophthalmic-patient.xlsx
+++ b/StructureDefinition-ophthalmic-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-patient.xlsx
+++ b/StructureDefinition-ophthalmic-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1751,17 +1751,17 @@
   <dimension ref="A1:AO64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.8359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.8359375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="56.515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.55859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1770,27 +1770,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.80859375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="85.70703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.0234375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="134.453125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="34.98828125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.76171875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="34.35546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="137.7109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="35.7421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="34.19921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.9296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-ophthalmic-patient.xlsx
+++ b/StructureDefinition-ophthalmic-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -494,7 +494,7 @@
     <t>Patients are almost always assigned specific numerical identifiers.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">pattern:type}
 </t>
   </si>
   <si>
@@ -603,7 +603,7 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
+    <t>Fixed to the National unique individual identifier type</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -613,6 +613,15 @@
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="NI"/&gt;
+    &lt;display value="National unique individual identifier"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>extensible</t>
@@ -3567,7 +3576,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
@@ -3604,7 +3613,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3619,13 +3628,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3643,7 +3652,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3667,7 +3676,7 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -3675,10 +3684,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3686,7 +3695,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
@@ -3704,16 +3713,16 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3723,10 +3732,10 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -3762,7 +3771,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3777,7 +3786,7 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -3786,7 +3795,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3794,10 +3803,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3823,13 +3832,13 @@
         <v>162</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3843,7 +3852,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -3879,7 +3888,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3894,7 +3903,7 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
@@ -3903,7 +3912,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -3911,10 +3920,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3937,13 +3946,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3994,7 +4003,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4009,7 +4018,7 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
@@ -4018,7 +4027,7 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4026,10 +4035,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4052,16 +4061,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4111,7 +4120,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4126,7 +4135,7 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
@@ -4135,7 +4144,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4143,13 +4152,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>147</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4262,7 +4271,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>161</v>
@@ -4377,7 +4386,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>168</v>
@@ -4494,7 +4503,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>174</v>
@@ -4613,7 +4622,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>185</v>
@@ -4624,7 +4633,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
@@ -4642,7 +4651,7 @@
         <v>186</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>188</v>
@@ -4661,7 +4670,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -4676,13 +4685,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4700,7 +4709,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4724,7 +4733,7 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -4732,10 +4741,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4761,16 +4770,16 @@
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4783,7 +4792,7 @@
         <v>82</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>82</v>
@@ -4819,7 +4828,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4834,7 +4843,7 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
@@ -4843,7 +4852,7 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4851,10 +4860,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4880,13 +4889,13 @@
         <v>162</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4900,7 +4909,7 @@
         <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>82</v>
@@ -4936,7 +4945,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4951,7 +4960,7 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -4960,7 +4969,7 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -4968,10 +4977,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4994,13 +5003,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5051,7 +5060,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5066,7 +5075,7 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -5075,7 +5084,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5083,10 +5092,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5109,16 +5118,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5168,7 +5177,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5183,7 +5192,7 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
@@ -5192,7 +5201,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5200,10 +5209,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5226,70 +5235,70 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q30" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="P30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q30" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="R30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5304,13 +5313,13 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>166</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>82</v>
@@ -5321,10 +5330,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5347,19 +5356,19 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5408,7 +5417,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5423,16 +5432,16 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5440,10 +5449,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5466,19 +5475,19 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5527,7 +5536,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5542,16 +5551,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5559,10 +5568,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5588,16 +5597,16 @@
         <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5625,10 +5634,10 @@
         <v>179</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5646,7 +5655,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5661,16 +5670,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5678,10 +5687,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5704,19 +5713,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5765,7 +5774,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5780,27 +5789,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5823,19 +5832,19 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5884,7 +5893,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5899,7 +5908,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>166</v>
@@ -5908,7 +5917,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -5916,10 +5925,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5942,19 +5951,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6003,7 +6012,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6018,16 +6027,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6035,10 +6044,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6064,14 +6073,14 @@
         <v>186</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6096,13 +6105,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6120,7 +6129,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6135,16 +6144,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6152,10 +6161,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6178,19 +6187,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6239,7 +6248,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6254,7 +6263,7 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>166</v>
@@ -6263,7 +6272,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6271,10 +6280,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6297,19 +6306,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6358,7 +6367,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6373,7 +6382,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>166</v>
@@ -6382,7 +6391,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6390,10 +6399,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6416,19 +6425,19 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6477,7 +6486,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6489,10 +6498,10 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>166</v>
@@ -6509,10 +6518,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6624,10 +6633,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6741,14 +6750,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6770,10 +6779,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>139</v>
@@ -6828,7 +6837,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6860,10 +6869,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6889,14 +6898,14 @@
         <v>186</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -6921,13 +6930,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -6945,7 +6954,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6960,7 +6969,7 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>166</v>
@@ -6969,7 +6978,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -6977,10 +6986,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7003,17 +7012,17 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7062,7 +7071,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7077,7 +7086,7 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>166</v>
@@ -7086,7 +7095,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7094,10 +7103,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7120,19 +7129,19 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7181,7 +7190,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7196,7 +7205,7 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>166</v>
@@ -7205,7 +7214,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7213,10 +7222,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7239,17 +7248,17 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7298,7 +7307,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7313,7 +7322,7 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>166</v>
@@ -7322,7 +7331,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7330,10 +7339,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7359,14 +7368,14 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7394,10 +7403,10 @@
         <v>179</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7415,7 +7424,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7430,7 +7439,7 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>166</v>
@@ -7439,7 +7448,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7447,10 +7456,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7473,17 +7482,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7532,7 +7541,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7541,13 +7550,13 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>166</v>
@@ -7556,7 +7565,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7564,10 +7573,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7590,13 +7599,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7647,7 +7656,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7662,7 +7671,7 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>166</v>
@@ -7679,10 +7688,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7705,19 +7714,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7766,7 +7775,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7781,10 +7790,10 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
@@ -7798,10 +7807,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7913,10 +7922,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8030,14 +8039,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8059,10 +8068,10 @@
         <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -8117,7 +8126,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8149,10 +8158,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8178,16 +8187,16 @@
         <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8236,7 +8245,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8251,16 +8260,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8268,10 +8277,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8294,19 +8303,19 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8355,7 +8364,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8370,16 +8379,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8387,14 +8396,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8413,16 +8422,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8472,7 +8481,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8487,7 +8496,7 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>166</v>
@@ -8496,7 +8505,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8504,10 +8513,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8530,19 +8539,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8591,7 +8600,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8606,10 +8615,10 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>82</v>
@@ -8623,10 +8632,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8649,19 +8658,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -8710,7 +8719,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8725,7 +8734,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>166</v>
@@ -8742,10 +8751,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8857,10 +8866,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8974,14 +8983,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9003,10 +9012,10 @@
         <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>139</v>
@@ -9061,7 +9070,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9093,10 +9102,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9119,16 +9128,16 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9178,7 +9187,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9202,7 +9211,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9210,10 +9219,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9239,10 +9248,10 @@
         <v>110</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9272,10 +9281,10 @@
         <v>179</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9293,7 +9302,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>90</v>
@@ -9308,7 +9317,7 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>166</v>
